--- a/esyluban/examples/release/DataTables/error/错误码.xlsx
+++ b/esyluban/examples/release/DataTables/error/错误码.xlsx
@@ -1411,7 +1411,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1966,7 +1966,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D2:F2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
